--- a/demo 2 (alpha)/Pb210_results/CA modeling data/elogpb210_zi_CA_summary.xlsx
+++ b/demo 2 (alpha)/Pb210_results/CA modeling data/elogpb210_zi_CA_summary.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.722118934927619</v>
+        <v>2.724494573930018</v>
       </c>
       <c r="D2">
-        <v>0.0696839541184533</v>
+        <v>0.07070441426454249</v>
       </c>
       <c r="E2">
-        <v>39.06378404274225</v>
+        <v>38.53358524032527</v>
       </c>
       <c r="F2">
-        <v>3.291440374243724E-29</v>
+        <v>5.118652750368747E-29</v>
       </c>
       <c r="G2">
-        <v>0.9425061257952883</v>
+        <v>0.9415119310767779</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.08149476221829645</v>
+        <v>-0.08194048895295264</v>
       </c>
       <c r="D3">
-        <v>0.003448813337841261</v>
+        <v>0.003499318172233773</v>
       </c>
       <c r="E3">
-        <v>-23.6297979145798</v>
+        <v>-23.41612992014565</v>
       </c>
       <c r="F3">
-        <v>2.957777691047545E-22</v>
+        <v>3.92670622709605E-22</v>
       </c>
       <c r="G3">
-        <v>0.9425061257952883</v>
+        <v>0.9415119310767779</v>
       </c>
     </row>
   </sheetData>
